--- a/excel-files/PARANAQUE/DON BOSCO HIGH SCHOOL PARAÑAQUE.xlsx
+++ b/excel-files/PARANAQUE/DON BOSCO HIGH SCHOOL PARAÑAQUE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AE6AC37-0FAD-4420-9F2F-19843BD5B22E}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{581FEFA2-13DE-4C32-BCFF-A320FA4D52A2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -811,6 +811,24 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3639,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3662,7 +3680,7 @@
     <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="50"/>
     </row>
     <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3744,7 +3762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3767,7 +3785,7 @@
     <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="50"/>
     </row>
     <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -3869,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3894,7 +3912,7 @@
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="51"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -3939,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -4084,7 +4102,7 @@
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="E30" s="51"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -4274,7 +4292,7 @@
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+      <c r="E40" s="51"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -4464,7 +4482,7 @@
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
+      <c r="E50" s="51"/>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -4482,7 +4500,7 @@
       <c r="D51" s="42">
         <v>535</v>
       </c>
-      <c r="E51" s="42">
+      <c r="E51" s="52">
         <v>2024</v>
       </c>
       <c r="F51" s="12" t="s">
@@ -4508,7 +4526,7 @@
         <v>488</v>
       </c>
       <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
+      <c r="E52" s="53"/>
       <c r="F52" s="12"/>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
@@ -4532,7 +4550,7 @@
       <c r="D53" s="44">
         <v>535</v>
       </c>
-      <c r="E53" s="44">
+      <c r="E53" s="54">
         <v>2024</v>
       </c>
       <c r="F53" s="12" t="s">
@@ -4558,7 +4576,7 @@
         <v>488</v>
       </c>
       <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
+      <c r="E54" s="53"/>
       <c r="F54" s="12"/>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
@@ -4582,7 +4600,7 @@
       <c r="D55" s="44">
         <v>535</v>
       </c>
-      <c r="E55" s="44">
+      <c r="E55" s="54">
         <v>2025</v>
       </c>
       <c r="F55" s="12" t="s">
@@ -4610,7 +4628,7 @@
       <c r="D56" s="44">
         <v>535</v>
       </c>
-      <c r="E56" s="44">
+      <c r="E56" s="54">
         <v>2024</v>
       </c>
       <c r="F56" s="12" t="s">
@@ -4638,7 +4656,7 @@
       <c r="D57" s="44">
         <v>535</v>
       </c>
-      <c r="E57" s="44">
+      <c r="E57" s="54">
         <v>2025</v>
       </c>
       <c r="F57" s="12" t="s">
@@ -4666,7 +4684,7 @@
       <c r="D58" s="44">
         <v>535</v>
       </c>
-      <c r="E58" s="44">
+      <c r="E58" s="54">
         <v>2025</v>
       </c>
       <c r="F58" s="12" t="s">
@@ -4694,7 +4712,7 @@
       <c r="D59" s="44">
         <v>535</v>
       </c>
-      <c r="E59" s="44">
+      <c r="E59" s="54">
         <v>2025</v>
       </c>
       <c r="F59" s="12" t="s">
@@ -4714,7 +4732,7 @@
       <c r="B60" s="7"/>
       <c r="C60" s="45"/>
       <c r="D60" s="45"/>
-      <c r="E60" s="45"/>
+      <c r="E60" s="55"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -4730,7 +4748,7 @@
         <v>480</v>
       </c>
       <c r="D61" s="43"/>
-      <c r="E61" s="43"/>
+      <c r="E61" s="53"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3">
         <f t="shared" ref="G61:G69" si="12">IF((C61-D61)&lt;0,0,C61-D61)</f>
@@ -4752,7 +4770,7 @@
         <v>480</v>
       </c>
       <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
+      <c r="E62" s="53"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3">
         <f t="shared" si="12"/>
@@ -4776,7 +4794,7 @@
       <c r="D63" s="44">
         <v>466</v>
       </c>
-      <c r="E63" s="44">
+      <c r="E63" s="54">
         <v>2025</v>
       </c>
       <c r="F63" s="12" t="s">
@@ -4804,7 +4822,7 @@
       <c r="D64" s="44">
         <v>466</v>
       </c>
-      <c r="E64" s="44">
+      <c r="E64" s="54">
         <v>2025</v>
       </c>
       <c r="F64" s="12" t="s">
@@ -4934,7 +4952,7 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+      <c r="E70" s="51"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -5124,7 +5142,7 @@
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
+      <c r="E80" s="51"/>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -5314,7 +5332,7 @@
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
+      <c r="E90" s="51"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -5486,11 +5504,11 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E65:E69 E91:E98 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E52:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6 E51" xr:uid="{441421B3-B33B-4DBC-9CB3-0FB490F57A42}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5502,7 +5520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -10109,12 +10127,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E73" s="43"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="12"/>
+      <c r="E73" s="44">
+        <v>68</v>
+      </c>
+      <c r="F73" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I73" s="12">
         <f t="shared" si="3"/>
@@ -10180,12 +10204,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E74" s="43"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="12"/>
+      <c r="E74" s="44">
+        <v>68</v>
+      </c>
+      <c r="F74" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I74" s="12">
         <f t="shared" si="3"/>
@@ -10252,7 +10282,7 @@
         <v>3840</v>
       </c>
       <c r="E75" s="44">
-        <v>466</v>
+        <v>68</v>
       </c>
       <c r="F75" s="10">
         <v>2025</v>
@@ -10262,7 +10292,7 @@
       </c>
       <c r="H75" s="12">
         <f t="shared" si="2"/>
-        <v>3374</v>
+        <v>3772</v>
       </c>
       <c r="I75" s="12">
         <f t="shared" si="3"/>
@@ -10329,7 +10359,7 @@
         <v>3840</v>
       </c>
       <c r="E76" s="44">
-        <v>466</v>
+        <v>68</v>
       </c>
       <c r="F76" s="10">
         <v>2025</v>
@@ -10339,7 +10369,7 @@
       </c>
       <c r="H76" s="12">
         <f t="shared" si="2"/>
-        <v>3374</v>
+        <v>3772</v>
       </c>
       <c r="I76" s="12">
         <f t="shared" si="3"/>
@@ -10405,12 +10435,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
+      <c r="E77" s="44">
+        <v>68</v>
+      </c>
+      <c r="F77" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H77" s="12">
         <f t="shared" si="2"/>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I77" s="12">
         <f t="shared" si="3"/>
@@ -10476,12 +10512,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="12"/>
+      <c r="E78" s="44">
+        <v>68</v>
+      </c>
+      <c r="F78" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H78" s="12">
         <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I78" s="12">
         <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
@@ -10547,12 +10589,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="12"/>
+      <c r="E79" s="44">
+        <v>68</v>
+      </c>
+      <c r="F79" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H79" s="12">
         <f t="shared" si="22"/>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I79" s="12">
         <f t="shared" si="23"/>
@@ -10618,12 +10666,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
+      <c r="E80" s="44">
+        <v>68</v>
+      </c>
+      <c r="F80" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H80" s="12">
         <f t="shared" si="22"/>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I80" s="12">
         <f t="shared" si="23"/>
@@ -10689,12 +10743,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3840</v>
       </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="12"/>
+      <c r="E81" s="44">
+        <v>68</v>
+      </c>
+      <c r="F81" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H81" s="12">
         <f t="shared" si="22"/>
-        <v>3840</v>
+        <v>3772</v>
       </c>
       <c r="I81" s="12">
         <f t="shared" si="23"/>
@@ -13619,191 +13679,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C112:C127 C5:C12 C83:C91 C93:C110" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D73:F81" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G83:G91 G93:G101 G103:G110 G73:G81" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13816,10 +13696,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G103:G110 G83:G91 G93:G101 G73:G81" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13835,7 +13715,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -22394,186 +22274,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D76:F77 D79:F80 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:V101 Z91:AA101 T103:V113 Z103:AA113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R91 N103:R103 D67:D75 F67:F75 D83:F89 D81:D82 F81:F82 N92:P101 N104:P113 H103:L113 H91:L101" name="LAS"/>
@@ -22599,8 +22299,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M103:M113 G91:G101 G103:G113 Y103:Y113 S103:S113 M115:M122 M91:M101" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 F103:F113 R91:R101 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L103:L113 R103:R113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 X91:X101 X103:X113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 L91:L101" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
